--- a/Capstone/Project Roadmap.xlsx
+++ b/Capstone/Project Roadmap.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="kDTQ3hmAo+BUZ+USxoTFVZ7QE5KFr0h1lmN5MiyX4D4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="SPaC5YflPd1nJfxDvMK0xRNWUjRlkC123Lc57kGRrvQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="37">
   <si>
     <t>Day</t>
   </si>
@@ -30,18 +30,27 @@
     <t>Comments</t>
   </si>
   <si>
+    <t>Owner</t>
+  </si>
+  <si>
     <t>PRD</t>
   </si>
   <si>
     <t>Done</t>
   </si>
   <si>
+    <t>Likhitha</t>
+  </si>
+  <si>
     <t>Github Repo</t>
   </si>
   <si>
     <t>Environment Setup</t>
   </si>
   <si>
+    <t>Both</t>
+  </si>
+  <si>
     <t>Design Doc Roadmap</t>
   </si>
   <si>
@@ -51,28 +60,40 @@
     <t>Market Research</t>
   </si>
   <si>
+    <t>Proteeti</t>
+  </si>
+  <si>
     <t>Evaluations</t>
   </si>
   <si>
     <t>Observability</t>
   </si>
   <si>
-    <t>Test backend code (FastAPI) end to end deployment, submit in Github, Code eval for the design choices</t>
+    <t>FastAPI implementation</t>
+  </si>
+  <si>
+    <t>Added LLM Evaluation Metrics and Prometheus logging</t>
+  </si>
+  <si>
+    <t>Streamlit End to End deployment: definition of all widgets</t>
+  </si>
+  <si>
+    <t>Prod Testing Scenarios</t>
   </si>
   <si>
     <t>Guardrails</t>
   </si>
   <si>
+    <t>FastAPI Integration</t>
+  </si>
+  <si>
+    <t>FastAPI Integration Testing</t>
+  </si>
+  <si>
     <t>Progress</t>
   </si>
   <si>
-    <t>Added LLM Evaluation Metrics and Prometheus logging</t>
-  </si>
-  <si>
-    <t>Streamlit End to End deployment: definition of all widgets</t>
-  </si>
-  <si>
-    <t>Prod Testing Scenarios</t>
+    <t>Input Document Validation</t>
   </si>
   <si>
     <t>Clean up Evaluations Display and Dashboard</t>
@@ -81,6 +102,9 @@
     <t>Gen UI CLeanup</t>
   </si>
   <si>
+    <t>Prototype Milestone</t>
+  </si>
+  <si>
     <t>VectorDB-&gt;PineCone</t>
   </si>
   <si>
@@ -90,10 +114,19 @@
     <t>Create Differentiator Upload page for all RAG projects</t>
   </si>
   <si>
-    <t>Polish for Production Level</t>
+    <t>Polish for Production Level (Ensure Langchain, Pinecone, OpenAI)</t>
+  </si>
+  <si>
+    <t>Final Manual Testing</t>
+  </si>
+  <si>
+    <t>Production Milestone</t>
   </si>
   <si>
     <t>Serve on Docker</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
   </si>
 </sst>
 </file>
@@ -124,7 +157,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -135,6 +168,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -151,8 +196,14 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -160,14 +211,8 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -385,7 +430,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="4.14"/>
+    <col customWidth="1" min="1" max="1" width="4.43"/>
     <col customWidth="1" min="2" max="2" width="82.71"/>
     <col customWidth="1" min="3" max="3" width="8.71"/>
     <col customWidth="1" min="4" max="4" width="28.43"/>
@@ -405,212 +450,334 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2">
         <v>1.0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="B7" s="3" t="s">
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="7">
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="8">
         <v>5.0</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
+      <c r="B26" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="E26" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
     <row r="27" ht="14.25" customHeight="1"/>
     <row r="28" ht="14.25" customHeight="1"/>
     <row r="29" ht="14.25" customHeight="1"/>
@@ -1571,10 +1738,11 @@
     <row r="984" ht="14.25" customHeight="1"/>
     <row r="985" ht="14.25" customHeight="1"/>
     <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A8"/>
-  </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Capstone/Project Roadmap.xlsx
+++ b/Capstone/Project Roadmap.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="SPaC5YflPd1nJfxDvMK0xRNWUjRlkC123Lc57kGRrvQ="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="rIn5HZsC23A+eY0ipR3265kfQGsDzj9lzz6UjQN2DmQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
   <si>
     <t>Day</t>
   </si>
@@ -114,6 +114,9 @@
     <t>Create Differentiator Upload page for all RAG projects</t>
   </si>
   <si>
+    <t>Implement Grafana</t>
+  </si>
+  <si>
     <t>Polish for Production Level (Ensure Langchain, Pinecone, OpenAI)</t>
   </si>
   <si>
@@ -127,6 +130,27 @@
   </si>
   <si>
     <t>Monitoring</t>
+  </si>
+  <si>
+    <t>Lgin page pending</t>
+  </si>
+  <si>
+    <t>Explain the number using Tavily</t>
+  </si>
+  <si>
+    <t>USe bullts in diff dectins f PRpsal</t>
+  </si>
+  <si>
+    <t>Add differentiatr pints</t>
+  </si>
+  <si>
+    <t>RAGAS eval</t>
+  </si>
+  <si>
+    <t>MAke mre catchy dem</t>
+  </si>
+  <si>
+    <t>cme up with mre scenaris</t>
   </si>
 </sst>
 </file>
@@ -656,39 +680,43 @@
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="8" t="s">
+      <c r="C17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="8" t="s">
+      <c r="C18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="5" t="s">
+      <c r="C19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -732,14 +760,16 @@
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="8" t="s">
-        <v>10</v>
+      <c r="C23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -748,9 +778,7 @@
         <v>33</v>
       </c>
       <c r="C24" s="6"/>
-      <c r="D24" s="5" t="s">
-        <v>34</v>
-      </c>
+      <c r="D24" s="6"/>
       <c r="E24" s="8" t="s">
         <v>10</v>
       </c>
@@ -758,36 +786,76 @@
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
       <c r="E25" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="B26" s="8" t="s">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="8"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
       <c r="E26" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="E27" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
     <row r="28" ht="14.25" customHeight="1"/>
     <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="B30" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="B31" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="B32" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="B33" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="B34" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="B35" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="B36" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="37" ht="14.25" customHeight="1"/>
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
@@ -1742,6 +1810,7 @@
     <row r="988" ht="14.25" customHeight="1"/>
     <row r="989" ht="14.25" customHeight="1"/>
     <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
